--- a/project/excel/brc_schema.xlsx
+++ b/project/excel/brc_schema.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,11 @@
         </is>
       </c>
       <c r="C1" t="inlineStr">
+        <is>
+          <t>taxon_ids</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>strains</t>
         </is>

--- a/project/excel/brc_schema.xlsx
+++ b/project/excel/brc_schema.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DatasetCollection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dataset" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Individual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="OntologyAnnotation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Contributor" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Funding" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="BRCOrganization" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Organism" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Plasmid" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="RelatedItem" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MediaSet" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="MediaFile" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DatasetCollection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Individual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OntologyAnnotation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contributor" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRCOrganization" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organism" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plasmid" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelatedItem" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MediaSet" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MediaFile" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
